--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20211.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -73,34 +73,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>HERAS</t>
-  </si>
-  <si>
-    <t>CHORA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>CESAR ENRIQUE</t>
-  </si>
-  <si>
-    <t>GABRIEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>NADYA GUADALUPE</t>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>JESUS</t>
   </si>
 </sst>
 </file>
@@ -501,19 +489,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -527,19 +515,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>65.38</v>
+        <v>92.31</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -592,16 +580,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="H2">
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -615,16 +606,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.45999999999999</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -677,19 +671,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -703,19 +697,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>65.38</v>
+        <v>92.31</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -725,7 +719,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -757,16 +751,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920347</v>
+        <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -775,76 +769,30 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920235</v>
+        <v>20330051920346</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920227</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920239</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20211.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20211.xlsx
@@ -769,7 +769,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -792,7 +792,7 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20211.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -73,22 +73,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>ADAN</t>
-  </si>
-  <si>
-    <t>JESUS</t>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
   </si>
 </sst>
 </file>
@@ -580,19 +571,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -606,19 +597,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>88.45999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -683,7 +674,7 @@
         <v>72</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -700,16 +691,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>92.31</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +710,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -751,16 +742,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920337</v>
+        <v>20330051920336</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -769,29 +760,6 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920346</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
         <v>1</v>
       </c>
     </row>
